--- a/ExcelDetails/SessionExcel.xlsx
+++ b/ExcelDetails/SessionExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -184,6 +184,33 @@
   </si>
   <si>
     <t>Prompt Engg PPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Done with Invoice Extractor App </t>
+  </si>
+  <si>
+    <t>Done with Multipleways to connect OpenAI, ChatClient, ResponseClient and OpenAIclient</t>
+  </si>
+  <si>
+    <t>Done With Chat and Chat ConversionId. Understand how LLM use memory.</t>
+  </si>
+  <si>
+    <t>&amp;R3z2V^M</t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/rec/share/40NGIXZl2ca5xfmxeUPQ5rMrH5DuR2j1sDhlx9dcI6X3DkeVXqW1zZcge6OIJcuJ.JNFf43VEWf1rICEb</t>
+  </si>
+  <si>
+    <t>490$ch*C</t>
+  </si>
+  <si>
+    <t> https://us06web.zoom.us/rec/share/VsNS9yfjeiwoVhZZ_yvjY49o86dR1LOIa8lGiHMUx84nstPASy_9-y_enlCANPQW.ZfMKuV-ypV2lSfFN</t>
+  </si>
+  <si>
+    <t>EducationAIAgent/Session6 at develop · deveshomar/EducationAIAgent</t>
+  </si>
+  <si>
+    <t>EducationAIAgent/Session5 at develop · deveshomar/EducationAIAgent</t>
   </si>
 </sst>
 </file>
@@ -312,7 +339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -339,32 +366,33 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -646,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -691,7 +719,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
+      <c r="A4" s="14">
         <v>37104</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -731,25 +759,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+    <row r="6" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="18">
         <v>37469</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="21" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -773,8 +801,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="19"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
@@ -789,8 +817,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="C9" s="20"/>
+      <c r="A9" s="20"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="1" t="s">
         <v>37</v>
       </c>
@@ -850,22 +878,22 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-    </row>
-    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
+    <row r="16" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
         <v>40026</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -878,8 +906,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
       <c r="C18" s="6" t="s">
         <v>44</v>
       </c>
@@ -890,8 +918,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="20"/>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
@@ -900,6 +928,46 @@
       </c>
       <c r="E19" s="9" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>42217</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <v>42583</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -924,8 +992,12 @@
     <hyperlink ref="E17" r:id="rId13" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
     <hyperlink ref="E18" r:id="rId14" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
     <hyperlink ref="E19" r:id="rId15" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
+    <hyperlink ref="F26" r:id="rId16"/>
+    <hyperlink ref="F22" r:id="rId17" display="https://us06web.zoom.us/rec/share/VsNS9yfjeiwoVhZZ_yvjY49o86dR1LOIa8lGiHMUx84nstPASy_9-y_enlCANPQW.ZfMKuV-ypV2lSfFN"/>
+    <hyperlink ref="D26" r:id="rId18" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session6"/>
+    <hyperlink ref="D22" r:id="rId19" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
--- a/ExcelDetails/SessionExcel.xlsx
+++ b/ExcelDetails/SessionExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
   <si>
     <t>Date</t>
   </si>
@@ -211,6 +211,39 @@
   </si>
   <si>
     <t>EducationAIAgent/Session5 at develop · deveshomar/EducationAIAgent</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>done with AI agent first session</t>
+  </si>
+  <si>
+    <t>AiAgents with c#, tool calling</t>
+  </si>
+  <si>
+    <t>learned  human in loop in Write Tools</t>
+  </si>
+  <si>
+    <t>learned  about Problems if we rely on Agents for Auto function calling</t>
+  </si>
+  <si>
+    <t>learned about Best Tool calling practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">learned about Read and write tools </t>
+  </si>
+  <si>
+    <t>learned  Intent classifer</t>
+  </si>
+  <si>
+    <t>Done with Supervisor Agent</t>
+  </si>
+  <si>
+    <t>done with MultiAgent app with Parellel agent calling</t>
+  </si>
+  <si>
+    <t>Learned about Task.when all</t>
   </si>
 </sst>
 </file>
@@ -374,6 +407,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -392,7 +426,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -674,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
@@ -774,10 +807,10 @@
       <c r="L6" s="15"/>
     </row>
     <row r="7" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="19">
         <v>37469</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="22" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -801,8 +834,8 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="C8" s="22"/>
+      <c r="A8" s="20"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
@@ -817,8 +850,8 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="21"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="1" t="s">
         <v>37</v>
       </c>
@@ -893,7 +926,7 @@
       <c r="L16" s="15"/>
     </row>
     <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
+      <c r="A17" s="19">
         <v>40026</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -907,7 +940,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
+      <c r="A18" s="20"/>
       <c r="C18" s="6" t="s">
         <v>44</v>
       </c>
@@ -919,7 +952,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
+      <c r="A19" s="21"/>
       <c r="C19" s="1" t="s">
         <v>45</v>
       </c>
@@ -937,10 +970,10 @@
       <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="18" t="s">
         <v>56</v>
       </c>
       <c r="G22" s="10" t="s">
@@ -960,14 +993,91 @@
       <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="18" t="s">
         <v>54</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>45139</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>45505</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C31" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
+        <v>47331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
+        <v>11171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
+        <v>38596</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
+        <v>38961</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelDetails/SessionExcel.xlsx
+++ b/ExcelDetails/SessionExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Learned about Task.when all</t>
+  </si>
+  <si>
+    <t>EducationAIAgent/Session10 at develop · deveshomar/EducationAIAgent</t>
+  </si>
+  <si>
+    <t>EducationAIAgent/Session9 at develop · deveshomar/EducationAIAgent</t>
   </si>
 </sst>
 </file>
@@ -372,7 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -426,6 +432,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -712,8 +722,8 @@
   <cols>
     <col min="1" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="85.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="53.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.88671875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="112.44140625" style="25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.33203125" style="1" customWidth="1"/>
@@ -726,7 +736,7 @@
       <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="25" t="s">
         <v>21</v>
       </c>
     </row>
@@ -739,7 +749,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="26"/>
       <c r="F2" s="8" t="s">
         <v>4</v>
       </c>
@@ -761,7 +771,7 @@
       <c r="D4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="27" t="s">
         <v>40</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -778,11 +788,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="27" t="s">
         <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -797,7 +807,7 @@
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="16"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -806,7 +816,7 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>37469</v>
       </c>
@@ -816,7 +826,7 @@
       <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="27" t="s">
         <v>34</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -833,13 +843,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="20"/>
       <c r="C8" s="23"/>
       <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="27" t="s">
         <v>36</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -849,20 +859,20 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="21"/>
       <c r="C9" s="24"/>
       <c r="D9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="27" t="s">
         <v>38</v>
       </c>
       <c r="F9" s="12"/>
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="E10" s="9"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="12"/>
       <c r="H10" s="13"/>
     </row>
@@ -876,7 +886,7 @@
       <c r="D11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="27" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -892,22 +902,22 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="27" t="s">
         <v>28</v>
       </c>
     </row>
@@ -916,7 +926,7 @@
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
+      <c r="E16" s="28"/>
       <c r="F16" s="16"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
@@ -925,7 +935,7 @@
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
     </row>
-    <row r="17" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
         <v>40026</v>
       </c>
@@ -935,7 +945,7 @@
       <c r="D17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -947,11 +957,11 @@
       <c r="D18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="21"/>
       <c r="C19" s="1" t="s">
         <v>45</v>
@@ -959,7 +969,7 @@
       <c r="D19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -970,7 +980,7 @@
       <c r="C22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="18" t="s">
@@ -993,7 +1003,7 @@
       <c r="C26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="E26" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F26" s="18" t="s">
@@ -1024,45 +1034,53 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>47331</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>11171</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>38596</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E39" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C40" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C41" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C42" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C43" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E44" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>38961</v>
       </c>
@@ -1070,12 +1088,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C46" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C47" s="1" t="s">
         <v>69</v>
       </c>
@@ -1104,10 +1122,12 @@
     <hyperlink ref="E19" r:id="rId15" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session4"/>
     <hyperlink ref="F26" r:id="rId16"/>
     <hyperlink ref="F22" r:id="rId17" display="https://us06web.zoom.us/rec/share/VsNS9yfjeiwoVhZZ_yvjY49o86dR1LOIa8lGiHMUx84nstPASy_9-y_enlCANPQW.ZfMKuV-ypV2lSfFN"/>
-    <hyperlink ref="D26" r:id="rId18" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session6"/>
-    <hyperlink ref="D22" r:id="rId19" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session5"/>
+    <hyperlink ref="E26" r:id="rId18" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session6"/>
+    <hyperlink ref="E22" r:id="rId19" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session5"/>
+    <hyperlink ref="E44" r:id="rId20" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session10"/>
+    <hyperlink ref="E39" r:id="rId21" display="https://github.com/deveshomar/EducationAIAgent/tree/develop/Session9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>